--- a/week-04/Simsek_Iowa_SWOT.xlsx
+++ b/week-04/Simsek_Iowa_SWOT.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sultansimsek/Desktop/DataAnalytics/week-04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5EE28D8-3738-664E-B1B6-EC133860774E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C66BE83-06F0-F14B-94FC-A688BF5A93C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="1" activeTab="2" xr2:uid="{6795345C-CB35-0348-AC27-4BEECCE4F135}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="5" xr2:uid="{6795345C-CB35-0348-AC27-4BEECCE4F135}"/>
   </bookViews>
   <sheets>
     <sheet name="S-%50 of revenue" sheetId="1" r:id="rId1"/>
@@ -1943,48 +1943,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
@@ -2016,48 +1974,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
@@ -2085,48 +2001,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
@@ -2156,48 +2030,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="4"/>
@@ -2227,48 +2059,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
@@ -2298,48 +2088,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="6"/>
@@ -2370,48 +2118,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="7"/>
@@ -2442,48 +2148,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="8"/>
@@ -2520,48 +2184,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="9"/>
@@ -2591,48 +2213,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="10"/>
@@ -2662,48 +2242,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2760,62 +2298,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -2963,62 +2446,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -3162,62 +2590,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -3363,62 +2736,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -3564,62 +2882,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -3765,62 +3028,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -3967,62 +3175,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -4169,62 +3322,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -4377,62 +3475,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -4578,62 +3621,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -4779,62 +3767,7 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
@@ -5346,34 +4279,34 @@
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>CANADIAN WHISKIES</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>80 PROOF VODKA</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>BLENDED WHISKIES</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>CANADIAN WHISKIES</c:v>
+                  <c:v>SPICED RUM</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>IMPORTED VODKA</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>PUERTO RICO &amp; VIRGIN ISLANDS RUM</c:v>
+                  <c:v>TEQUILA</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>SPICED RUM</c:v>
+                  <c:v>STRAIGHT BOURBON WHISKIES</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>STRAIGHT BOURBON WHISKIES</c:v>
+                  <c:v>WHISKEY LIQUEUR</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>TENNESSEE WHISKIES</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>TEQUILA</c:v>
+                  <c:v>PUERTO RICO &amp; VIRGIN ISLANDS RUM</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>WHISKEY LIQUEUR</c:v>
+                  <c:v>BLENDED WHISKIES</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5385,34 +4318,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>2906800.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>6963649.9800000004</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>92084.54</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>2906800.2</c:v>
+                  <c:v>54876.42</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1140</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>193326</c:v>
+                  <c:v>1571728.53</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>54876.42</c:v>
+                  <c:v>2735367.09</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2735367.09</c:v>
+                  <c:v>13217102.539999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1571728.53</c:v>
+                  <c:v>193326</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13217102.539999999</c:v>
+                  <c:v>92084.54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5456,34 +4389,34 @@
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>CANADIAN WHISKIES</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>80 PROOF VODKA</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>BLENDED WHISKIES</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>CANADIAN WHISKIES</c:v>
+                  <c:v>SPICED RUM</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>IMPORTED VODKA</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>PUERTO RICO &amp; VIRGIN ISLANDS RUM</c:v>
+                  <c:v>TEQUILA</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>SPICED RUM</c:v>
+                  <c:v>STRAIGHT BOURBON WHISKIES</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>STRAIGHT BOURBON WHISKIES</c:v>
+                  <c:v>WHISKEY LIQUEUR</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>TENNESSEE WHISKIES</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>TEQUILA</c:v>
+                  <c:v>PUERTO RICO &amp; VIRGIN ISLANDS RUM</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>WHISKEY LIQUEUR</c:v>
+                  <c:v>BLENDED WHISKIES</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5495,34 +4428,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>48053061.909999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>48045532.509999998</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>12037250.550000001</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>48053061.909999996</c:v>
+                  <c:v>31600618.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>23879524.629999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12729072.76</c:v>
+                  <c:v>21411263.640000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>31600618.5</c:v>
+                  <c:v>20924480.190000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20924480.190000001</c:v>
+                  <c:v>19339201.420000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>17647970.350000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>21411263.640000001</c:v>
+                  <c:v>12729072.76</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19339201.420000002</c:v>
+                  <c:v>12037250.550000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6378,64 +5311,64 @@
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>4095</c:v>
+                  <c:v>4994</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>4657</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>4503</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>4529</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>4657</c:v>
+                  <c:v>4765</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4716</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4765</c:v>
+                  <c:v>4529</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>4961</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4095</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>4834</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
+                  <c:v>5006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5069</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5094</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5086</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5016</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5081</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5082</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5078</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5079</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5056</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>4871</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4961</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4994</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5006</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5016</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5056</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5069</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5078</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>5079</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5081</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5082</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5086</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5094</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6447,46 +5380,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>12741.48</c:v>
+                  <c:v>27700.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>26733.439999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>24571.08</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>15276.58</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>26733.439999999999</c:v>
+                  <c:v>24421.95</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>16240.92</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24421.95</c:v>
+                  <c:v>15276.58</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>13712.15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12741.48</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>9825.56</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>1098.45</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13712.15</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>27700.1</c:v>
+                  <c:v>5997.65</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5997.65</c:v>
+                  <c:v>4858.8900000000003</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>4794.6400000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4528.68</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>3740.73</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1233.3399999999999</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4858.8900000000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>3556.53</c:v>
@@ -6501,10 +5434,10 @@
                   <c:v>3556.53</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4528.68</c:v>
+                  <c:v>1233.3399999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4794.6400000000003</c:v>
+                  <c:v>1098.45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6545,64 +5478,64 @@
               <c:strCache>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>4095</c:v>
+                  <c:v>4994</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>4657</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>4503</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>4529</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>4657</c:v>
+                  <c:v>4765</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4716</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4765</c:v>
+                  <c:v>4529</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>4961</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4095</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>4834</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
+                  <c:v>5006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5069</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5094</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5086</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5016</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5081</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5082</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5078</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5079</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5056</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>4871</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4961</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4994</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5006</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5016</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5056</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5069</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5078</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>5079</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5081</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5082</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5086</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5094</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6614,46 +5547,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>187.76</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>156.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>44.58</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>161.63999999999999</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>156.12</c:v>
+                  <c:v>22.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>80.16</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.32</c:v>
+                  <c:v>161.63999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187.76</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>44.58</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>164.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>96</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>64</c:v>
+                  <c:v>166.88</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>166.88</c:v>
+                  <c:v>104.82</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>104.82</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44.58</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.16</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>104.82</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>104.82</c:v>
@@ -6668,10 +5601,10 @@
                   <c:v>104.82</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>44.58</c:v>
+                  <c:v>89.16</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>104.82</c:v>
+                  <c:v>164.52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13181,8 +12114,8 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>138739</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15945,7 +14878,7 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B080B5E-7DBD-E640-BCFF-87E2279CBB10}" name="PivotTable9" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A14:C25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="11">
         <item x="1"/>
         <item x="9"/>
@@ -15959,6 +14892,15 @@
         <item x="6"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -15968,34 +14910,34 @@
   </rowFields>
   <rowItems count="11">
     <i>
+      <x v="2"/>
+    </i>
+    <i>
       <x/>
     </i>
     <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
+      <x v="5"/>
     </i>
     <i>
       <x v="3"/>
     </i>
     <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
+      <x v="8"/>
     </i>
     <i>
       <x v="6"/>
     </i>
     <i>
+      <x v="9"/>
+    </i>
+    <i>
       <x v="7"/>
     </i>
     <i>
-      <x v="8"/>
+      <x v="4"/>
     </i>
     <i>
-      <x v="9"/>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -16052,30 +14994,39 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD518BC3-8DC8-8F4A-8486-4F9E9C33ECCA}" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="G3:I24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="21">
+        <item x="12"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="10"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="18"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="17"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="3"/>
         <item x="19"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="15"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="17"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="10"/>
-        <item x="14"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="12"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -16092,46 +15043,13 @@
   </rowFields>
   <rowItems count="21">
     <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
       <x v="10"/>
     </i>
     <i>
-      <x v="11"/>
+      <x v="16"/>
     </i>
     <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
+      <x v="18"/>
     </i>
     <i>
       <x v="14"/>
@@ -16140,16 +15058,49 @@
       <x v="15"/>
     </i>
     <i>
-      <x v="16"/>
-    </i>
-    <i>
       <x v="17"/>
     </i>
     <i>
-      <x v="18"/>
+      <x v="11"/>
     </i>
     <i>
       <x v="19"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="12"/>
     </i>
     <i t="grand">
       <x/>
@@ -20383,8 +19334,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.5" bestFit="1" customWidth="1"/>
@@ -20568,35 +19519,35 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B15" s="4">
-        <v>6963649.9800000004</v>
+        <v>2906800.2</v>
       </c>
       <c r="C15" s="4">
-        <v>48045532.509999998</v>
+        <v>48053061.909999996</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B16" s="4">
-        <v>92084.54</v>
+        <v>6963649.9800000004</v>
       </c>
       <c r="C16" s="4">
-        <v>12037250.550000001</v>
+        <v>48045532.509999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B17" s="4">
-        <v>2906800.2</v>
+        <v>54876.42</v>
       </c>
       <c r="C17" s="4">
-        <v>48053061.909999996</v>
+        <v>31600618.5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -20612,35 +19563,35 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B19" s="4">
-        <v>193326</v>
+        <v>1571728.53</v>
       </c>
       <c r="C19" s="4">
-        <v>12729072.76</v>
+        <v>21411263.640000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B20" s="4">
-        <v>54876.42</v>
+        <v>2735367.09</v>
       </c>
       <c r="C20" s="4">
-        <v>31600618.5</v>
+        <v>20924480.190000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B21" s="4">
-        <v>2735367.09</v>
+        <v>13217102.539999999</v>
       </c>
       <c r="C21" s="4">
-        <v>20924480.190000001</v>
+        <v>19339201.420000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -20656,24 +19607,24 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B23" s="4">
-        <v>1571728.53</v>
+        <v>193326</v>
       </c>
       <c r="C23" s="4">
-        <v>21411263.640000001</v>
+        <v>12729072.76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B24" s="4">
-        <v>13217102.539999999</v>
+        <v>92084.54</v>
       </c>
       <c r="C24" s="4">
-        <v>19339201.420000002</v>
+        <v>12037250.550000001</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -22535,13 +21486,13 @@
         <v>44.58</v>
       </c>
       <c r="G4" s="6">
-        <v>4095</v>
+        <v>4994</v>
       </c>
       <c r="H4" s="4">
-        <v>12741.48</v>
+        <v>27700.1</v>
       </c>
       <c r="I4" s="4">
-        <v>187.76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -22555,13 +21506,13 @@
         <v>44.58</v>
       </c>
       <c r="G5" s="6">
-        <v>4503</v>
+        <v>4657</v>
       </c>
       <c r="H5" s="4">
-        <v>24571.08</v>
+        <v>26733.439999999999</v>
       </c>
       <c r="I5" s="4">
-        <v>44.58</v>
+        <v>156.12</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -22575,13 +21526,13 @@
         <v>60</v>
       </c>
       <c r="G6" s="6">
-        <v>4529</v>
+        <v>4503</v>
       </c>
       <c r="H6" s="4">
-        <v>15276.58</v>
+        <v>24571.08</v>
       </c>
       <c r="I6" s="4">
-        <v>161.63999999999999</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -22595,13 +21546,13 @@
         <v>64</v>
       </c>
       <c r="G7" s="6">
-        <v>4657</v>
+        <v>4765</v>
       </c>
       <c r="H7" s="4">
-        <v>26733.439999999999</v>
+        <v>24421.95</v>
       </c>
       <c r="I7" s="4">
-        <v>156.12</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -22635,13 +21586,13 @@
         <v>89.16</v>
       </c>
       <c r="G9" s="6">
-        <v>4765</v>
+        <v>4529</v>
       </c>
       <c r="H9" s="4">
-        <v>24421.95</v>
+        <v>15276.58</v>
       </c>
       <c r="I9" s="4">
-        <v>22.32</v>
+        <v>161.63999999999999</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -22655,13 +21606,13 @@
         <v>96</v>
       </c>
       <c r="G10" s="6">
-        <v>4834</v>
+        <v>4961</v>
       </c>
       <c r="H10" s="4">
-        <v>9825.56</v>
+        <v>13712.15</v>
       </c>
       <c r="I10" s="4">
-        <v>44.58</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -22675,13 +21626,13 @@
         <v>104.82</v>
       </c>
       <c r="G11" s="6">
-        <v>4871</v>
+        <v>4095</v>
       </c>
       <c r="H11" s="4">
-        <v>1098.45</v>
+        <v>12741.48</v>
       </c>
       <c r="I11" s="4">
-        <v>164.52</v>
+        <v>187.76</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -22695,13 +21646,13 @@
         <v>104.82</v>
       </c>
       <c r="G12" s="6">
-        <v>4961</v>
+        <v>4834</v>
       </c>
       <c r="H12" s="4">
-        <v>13712.15</v>
+        <v>9825.56</v>
       </c>
       <c r="I12" s="4">
-        <v>96</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -22715,13 +21666,13 @@
         <v>104.82</v>
       </c>
       <c r="G13" s="6">
-        <v>4994</v>
+        <v>5006</v>
       </c>
       <c r="H13" s="4">
-        <v>27700.1</v>
+        <v>5997.65</v>
       </c>
       <c r="I13" s="4">
-        <v>64</v>
+        <v>166.88</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
@@ -22735,13 +21686,13 @@
         <v>104.82</v>
       </c>
       <c r="G14" s="6">
-        <v>5006</v>
+        <v>5069</v>
       </c>
       <c r="H14" s="4">
-        <v>5997.65</v>
+        <v>4858.8900000000003</v>
       </c>
       <c r="I14" s="4">
-        <v>166.88</v>
+        <v>104.82</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
@@ -22755,13 +21706,13 @@
         <v>104.82</v>
       </c>
       <c r="G15" s="6">
-        <v>5016</v>
+        <v>5094</v>
       </c>
       <c r="H15" s="4">
-        <v>3740.73</v>
+        <v>4794.6400000000003</v>
       </c>
       <c r="I15" s="4">
-        <v>60</v>
+        <v>104.82</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -22775,13 +21726,13 @@
         <v>104.82</v>
       </c>
       <c r="G16" s="6">
-        <v>5056</v>
+        <v>5086</v>
       </c>
       <c r="H16" s="4">
-        <v>1233.3399999999999</v>
+        <v>4528.68</v>
       </c>
       <c r="I16" s="4">
-        <v>89.16</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
@@ -22795,13 +21746,13 @@
         <v>156.12</v>
       </c>
       <c r="G17" s="6">
-        <v>5069</v>
+        <v>5016</v>
       </c>
       <c r="H17" s="4">
-        <v>4858.8900000000003</v>
+        <v>3740.73</v>
       </c>
       <c r="I17" s="4">
-        <v>104.82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -22815,7 +21766,7 @@
         <v>161.63999999999999</v>
       </c>
       <c r="G18" s="6">
-        <v>5078</v>
+        <v>5081</v>
       </c>
       <c r="H18" s="4">
         <v>3556.53</v>
@@ -22835,7 +21786,7 @@
         <v>164.52</v>
       </c>
       <c r="G19" s="6">
-        <v>5079</v>
+        <v>5082</v>
       </c>
       <c r="H19" s="4">
         <v>3556.53</v>
@@ -22855,7 +21806,7 @@
         <v>166.88</v>
       </c>
       <c r="G20" s="6">
-        <v>5081</v>
+        <v>5078</v>
       </c>
       <c r="H20" s="4">
         <v>3556.53</v>
@@ -22875,7 +21826,7 @@
         <v>187.76</v>
       </c>
       <c r="G21" s="6">
-        <v>5082</v>
+        <v>5079</v>
       </c>
       <c r="H21" s="4">
         <v>3556.53</v>
@@ -22886,24 +21837,24 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G22" s="6">
-        <v>5086</v>
+        <v>5056</v>
       </c>
       <c r="H22" s="4">
-        <v>4528.68</v>
+        <v>1233.3399999999999</v>
       </c>
       <c r="I22" s="4">
-        <v>44.58</v>
+        <v>89.16</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="G23" s="6">
-        <v>5094</v>
+        <v>4871</v>
       </c>
       <c r="H23" s="4">
-        <v>4794.6400000000003</v>
+        <v>1098.45</v>
       </c>
       <c r="I23" s="4">
-        <v>104.82</v>
+        <v>164.52</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22911,7 +21862,7 @@
         <v>114</v>
       </c>
       <c r="H24" s="4">
-        <v>211701.76000000001</v>
+        <v>211701.75999999998</v>
       </c>
       <c r="I24" s="4">
         <v>2011.2199999999996</v>
